--- a/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T21:21:27+00:00</t>
+    <t>2026-10-11T19:39:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T19:39:36+00:00</t>
+    <t>2026-10-12T11:53:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
